--- a/data/06 - BD FACTURAS.xlsx
+++ b/data/06 - BD FACTURAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://formabyte-my.sharepoint.com/personal/econdor_formabyte_onmicrosoft_com/Documents/PRACTICAS/PRACTICAS EXCEL/EXCEL TABLAS DINAMICAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edwar Cruz\Documents\GitHub\PowerBi-Projects\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{33091336-EDDD-42F1-A81C-B5BEE14762DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE2C7A9-576C-4753-8885-815909689643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11924" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FACTURAS" sheetId="2" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -177,7 +180,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -215,14 +218,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -232,7 +235,42 @@
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -243,6 +281,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4659A66F-8284-4E49-B4F9-C7D80BDBA3EC}" name="T_Facturas" displayName="T_Facturas" ref="A1:L779" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:L779" xr:uid="{4659A66F-8284-4E49-B4F9-C7D80BDBA3EC}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{460831BA-61CD-45B8-BA5F-C9714495DD6D}" name="NUMERO FACTURA CLIENTE" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{B6F74E2A-8761-4EA4-BB34-2AF82AAC2C2A}" name="CONCEPTO"/>
+    <tableColumn id="3" xr3:uid="{2A172FD2-9130-4991-BB70-851C8BE4FB5D}" name="CLIENTE"/>
+    <tableColumn id="4" xr3:uid="{BF978408-A5A6-4430-AC4B-9DC8418CB1CE}" name="PROVINCIA"/>
+    <tableColumn id="5" xr3:uid="{AE5A33AD-5B31-4542-BD74-530A0276F9CE}" name="SECTOR"/>
+    <tableColumn id="6" xr3:uid="{DAB0BC66-3EFC-458D-8559-BB00E5B174F9}" name="IMPORTE CLIENTE" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{B059BD44-B5ED-4E6D-AFA3-E68787E8E28E}" name="FECHA FACTURA CLIENTE" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{846E5E94-036B-4F94-A07A-27EFADBFD932}" name="PAGADA CLIENTE" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{66B1DDBB-77A5-4ED4-BF5F-31BA5C0E8635}" name="PROVEEDOR"/>
+    <tableColumn id="10" xr3:uid="{0EE1438C-87CE-4F7C-B375-CA3413A56CC0}" name="ZONA"/>
+    <tableColumn id="11" xr3:uid="{133B0B53-13EE-4BC2-B1F5-E21C6E8EC305}" name="TIPO"/>
+    <tableColumn id="12" xr3:uid="{F4C22CEB-DC30-44B3-9FCD-7715C06FF6F1}" name="IMPORTE PROVEEDOR" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -567,17 +626,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L827"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="12.7" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" customWidth="1"/>
+    <col min="10" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="38.049999999999997" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -653,7 +717,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -691,7 +755,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -729,7 +793,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -767,7 +831,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -805,7 +869,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -843,7 +907,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -881,7 +945,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -919,7 +983,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -957,7 +1021,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -995,7 +1059,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1033,7 +1097,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1071,7 +1135,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1109,7 +1173,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1147,7 +1211,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1185,7 +1249,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -1223,7 +1287,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -1261,7 +1325,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -1299,7 +1363,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -1337,7 +1401,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -1375,7 +1439,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -1413,7 +1477,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -1451,7 +1515,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -1489,7 +1553,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1527,7 +1591,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -1565,7 +1629,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -1603,7 +1667,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -1641,7 +1705,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -1679,7 +1743,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -1717,7 +1781,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -1755,7 +1819,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -1793,7 +1857,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -1831,7 +1895,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -1869,7 +1933,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -1907,7 +1971,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -1945,7 +2009,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -1983,7 +2047,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -2021,7 +2085,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2059,7 +2123,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -2097,7 +2161,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2135,7 +2199,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -2173,7 +2237,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2211,7 +2275,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -2249,7 +2313,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -2287,7 +2351,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -2325,7 +2389,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2363,7 +2427,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -2401,7 +2465,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -2439,7 +2503,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -2477,7 +2541,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2515,7 +2579,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -2553,7 +2617,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -2591,7 +2655,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -2629,7 +2693,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -2667,7 +2731,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -2705,7 +2769,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -2743,7 +2807,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -2781,7 +2845,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -2819,7 +2883,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -2857,7 +2921,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -2895,7 +2959,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -2933,7 +2997,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -2971,7 +3035,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -3009,7 +3073,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -3047,7 +3111,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -3085,7 +3149,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -3123,7 +3187,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -3161,7 +3225,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -3199,7 +3263,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -3237,7 +3301,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -3275,7 +3339,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -3313,7 +3377,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -3351,7 +3415,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -3389,7 +3453,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -3427,7 +3491,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -3465,7 +3529,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3503,7 +3567,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -3541,7 +3605,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -3579,7 +3643,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -3617,7 +3681,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -3655,7 +3719,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -3693,7 +3757,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -3731,7 +3795,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -3769,7 +3833,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -3807,7 +3871,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -3845,7 +3909,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -3883,7 +3947,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -3921,7 +3985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -3959,7 +4023,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -3997,7 +4061,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -4035,7 +4099,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -4073,7 +4137,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -4111,7 +4175,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -4149,7 +4213,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -4187,7 +4251,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -4225,7 +4289,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -4263,7 +4327,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -4301,7 +4365,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -4339,7 +4403,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -4377,7 +4441,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -4415,7 +4479,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -4453,7 +4517,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -4491,7 +4555,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -4529,7 +4593,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -4567,7 +4631,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -4605,7 +4669,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -4643,7 +4707,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -4681,7 +4745,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -4719,7 +4783,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -4757,7 +4821,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -4795,7 +4859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -4833,7 +4897,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -4871,7 +4935,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -4909,7 +4973,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -4947,7 +5011,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -4985,7 +5049,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -5023,7 +5087,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -5061,7 +5125,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -5099,7 +5163,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -5137,7 +5201,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -5175,7 +5239,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -5213,7 +5277,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -5251,7 +5315,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -5289,7 +5353,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -5327,7 +5391,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -5365,7 +5429,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -5403,7 +5467,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -5441,7 +5505,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -5479,7 +5543,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -5517,7 +5581,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -5555,7 +5619,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -5593,7 +5657,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -5631,7 +5695,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -5669,7 +5733,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -5707,7 +5771,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -5745,7 +5809,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -5783,7 +5847,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -5821,7 +5885,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -5859,7 +5923,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -5897,7 +5961,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -5935,7 +5999,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -5973,7 +6037,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -6011,7 +6075,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -6049,7 +6113,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -6087,7 +6151,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -6125,7 +6189,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -6163,7 +6227,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -6201,7 +6265,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -6239,7 +6303,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -6277,7 +6341,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -6315,7 +6379,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -6353,7 +6417,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -6391,7 +6455,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -6429,7 +6493,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -6467,7 +6531,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -6505,7 +6569,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -6543,7 +6607,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -6581,7 +6645,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -6619,7 +6683,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -6657,7 +6721,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -6695,7 +6759,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -6733,7 +6797,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -6771,7 +6835,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -6809,7 +6873,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -6847,7 +6911,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -6885,7 +6949,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -6923,7 +6987,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -6961,7 +7025,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -6999,7 +7063,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -7037,7 +7101,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -7075,7 +7139,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -7113,7 +7177,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -7151,7 +7215,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -7189,7 +7253,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -7227,7 +7291,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -7265,7 +7329,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -7303,7 +7367,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -7341,7 +7405,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -7379,7 +7443,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -7417,7 +7481,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -7455,7 +7519,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -7493,7 +7557,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -7531,7 +7595,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -7569,7 +7633,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -7607,7 +7671,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -7645,7 +7709,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -7683,7 +7747,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -7721,7 +7785,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -7759,7 +7823,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -7797,7 +7861,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -7835,7 +7899,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -7873,7 +7937,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -7911,7 +7975,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -7949,7 +8013,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -7987,7 +8051,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -8025,7 +8089,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -8063,7 +8127,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -8101,7 +8165,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -8139,7 +8203,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -8177,7 +8241,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -8215,7 +8279,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -8253,7 +8317,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -8291,7 +8355,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -8329,7 +8393,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -8367,7 +8431,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -8405,7 +8469,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -8443,7 +8507,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -8481,7 +8545,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -8519,7 +8583,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -8557,7 +8621,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -8595,7 +8659,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -8633,7 +8697,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -8671,7 +8735,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -8709,7 +8773,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -8747,7 +8811,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -8785,7 +8849,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -8823,7 +8887,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -8861,7 +8925,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -8899,7 +8963,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -8937,7 +9001,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -8975,7 +9039,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -9013,7 +9077,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -9051,7 +9115,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -9089,7 +9153,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -9127,7 +9191,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -9165,7 +9229,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -9203,7 +9267,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -9241,7 +9305,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -9279,7 +9343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -9317,7 +9381,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -9355,7 +9419,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -9393,7 +9457,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -9431,7 +9495,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -9469,7 +9533,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -9507,7 +9571,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -9545,7 +9609,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -9583,7 +9647,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -9621,7 +9685,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -9659,7 +9723,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -9697,7 +9761,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -9735,7 +9799,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -9773,7 +9837,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -9811,7 +9875,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -9849,7 +9913,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -9887,7 +9951,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -9925,7 +9989,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -9963,7 +10027,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -10001,7 +10065,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -10039,7 +10103,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -10077,7 +10141,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -10115,7 +10179,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -10153,7 +10217,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -10191,7 +10255,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -10229,7 +10293,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -10267,7 +10331,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -10305,7 +10369,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -10343,7 +10407,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -10381,7 +10445,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -10419,7 +10483,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -10457,7 +10521,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -10495,7 +10559,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -10533,7 +10597,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -10571,7 +10635,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -10609,7 +10673,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -10647,7 +10711,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -10685,7 +10749,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -10723,7 +10787,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -10761,7 +10825,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -10799,7 +10863,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -10837,7 +10901,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -10875,7 +10939,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -10913,7 +10977,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -10951,7 +11015,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -10989,7 +11053,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -11027,7 +11091,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -11065,7 +11129,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -11103,7 +11167,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -11141,7 +11205,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -11179,7 +11243,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -11217,7 +11281,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -11255,7 +11319,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -11293,7 +11357,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -11331,7 +11395,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -11369,7 +11433,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -11407,7 +11471,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -11445,7 +11509,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -11483,7 +11547,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -11521,7 +11585,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -11559,7 +11623,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -11597,7 +11661,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -11635,7 +11699,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -11673,7 +11737,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -11711,7 +11775,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -11749,7 +11813,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -11787,7 +11851,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -11825,7 +11889,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -11863,7 +11927,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -11901,7 +11965,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -11939,7 +12003,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -11977,7 +12041,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -12015,7 +12079,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -12053,7 +12117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -12091,7 +12155,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -12129,7 +12193,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -12167,7 +12231,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -12205,7 +12269,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -12243,7 +12307,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -12281,7 +12345,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -12319,7 +12383,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -12357,7 +12421,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -12395,7 +12459,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -12433,7 +12497,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -12471,7 +12535,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -12509,7 +12573,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -12547,7 +12611,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -12585,7 +12649,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -12623,7 +12687,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -12661,7 +12725,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -12699,7 +12763,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -12737,7 +12801,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -12775,7 +12839,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -12813,7 +12877,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -12851,7 +12915,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -12889,7 +12953,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -12927,7 +12991,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -12965,7 +13029,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -13003,7 +13067,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -13041,7 +13105,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -13079,7 +13143,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -13117,7 +13181,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -13155,7 +13219,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -13193,7 +13257,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -13231,7 +13295,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -13269,7 +13333,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -13307,7 +13371,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -13345,7 +13409,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -13383,7 +13447,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -13421,7 +13485,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -13459,7 +13523,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -13497,7 +13561,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -13535,7 +13599,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -13573,7 +13637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -13611,7 +13675,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -13649,7 +13713,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -13687,7 +13751,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -13725,7 +13789,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -13763,7 +13827,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -13801,7 +13865,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -13839,7 +13903,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -13877,7 +13941,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -13915,7 +13979,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -13953,7 +14017,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -13991,7 +14055,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -14029,7 +14093,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -14067,7 +14131,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -14105,7 +14169,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -14143,7 +14207,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -14181,7 +14245,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -14219,7 +14283,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -14257,7 +14321,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -14295,7 +14359,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -14333,7 +14397,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -14371,7 +14435,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -14409,7 +14473,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -14447,7 +14511,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -14485,7 +14549,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -14523,7 +14587,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -14561,7 +14625,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -14599,7 +14663,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -14637,7 +14701,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -14675,7 +14739,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -14713,7 +14777,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -14751,7 +14815,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -14789,7 +14853,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -14827,7 +14891,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -14865,7 +14929,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -14903,7 +14967,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -14941,7 +15005,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -14979,7 +15043,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -15017,7 +15081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -15055,7 +15119,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -15093,7 +15157,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -15131,7 +15195,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -15169,7 +15233,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -15207,7 +15271,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -15245,7 +15309,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -15283,7 +15347,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -15321,7 +15385,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -15359,7 +15423,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -15397,7 +15461,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -15435,7 +15499,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -15473,7 +15537,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -15511,7 +15575,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -15549,7 +15613,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -15587,7 +15651,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -15625,7 +15689,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -15663,7 +15727,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -15701,7 +15765,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -15739,7 +15803,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -15777,7 +15841,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -15815,7 +15879,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -15853,7 +15917,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -15891,7 +15955,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -15929,7 +15993,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -15967,7 +16031,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -16005,7 +16069,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -16043,7 +16107,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -16081,7 +16145,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -16119,7 +16183,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -16157,7 +16221,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -16195,7 +16259,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -16233,7 +16297,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -16271,7 +16335,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -16309,7 +16373,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -16347,7 +16411,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -16385,7 +16449,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -16423,7 +16487,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -16461,7 +16525,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -16499,7 +16563,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -16537,7 +16601,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -16575,7 +16639,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -16613,7 +16677,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -16651,7 +16715,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -16689,7 +16753,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -16727,7 +16791,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -16765,7 +16829,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -16803,7 +16867,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -16841,7 +16905,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -16879,7 +16943,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -16917,7 +16981,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -16955,7 +17019,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -16993,7 +17057,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -17031,7 +17095,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -17069,7 +17133,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -17107,7 +17171,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -17145,7 +17209,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -17183,7 +17247,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -17221,7 +17285,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -17259,7 +17323,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440" s="4">
         <v>439</v>
       </c>
@@ -17297,7 +17361,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -17335,7 +17399,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442" s="4">
         <v>441</v>
       </c>
@@ -17373,7 +17437,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -17411,7 +17475,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444" s="4">
         <v>443</v>
       </c>
@@ -17449,7 +17513,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -17487,7 +17551,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A446" s="4">
         <v>445</v>
       </c>
@@ -17525,7 +17589,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -17563,7 +17627,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448" s="4">
         <v>447</v>
       </c>
@@ -17601,7 +17665,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449" s="4">
         <v>448</v>
       </c>
@@ -17639,7 +17703,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450" s="4">
         <v>449</v>
       </c>
@@ -17677,7 +17741,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -17715,7 +17779,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452" s="4">
         <v>451</v>
       </c>
@@ -17753,7 +17817,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -17791,7 +17855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454" s="4">
         <v>453</v>
       </c>
@@ -17829,7 +17893,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455" s="4">
         <v>454</v>
       </c>
@@ -17867,7 +17931,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A456" s="4">
         <v>455</v>
       </c>
@@ -17905,7 +17969,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -17943,7 +18007,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458" s="4">
         <v>457</v>
       </c>
@@ -17981,7 +18045,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" s="4">
         <v>458</v>
       </c>
@@ -18019,7 +18083,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460" s="4">
         <v>459</v>
       </c>
@@ -18057,7 +18121,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A461" s="4">
         <v>460</v>
       </c>
@@ -18095,7 +18159,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462" s="4">
         <v>461</v>
       </c>
@@ -18133,7 +18197,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
         <v>462</v>
       </c>
@@ -18171,7 +18235,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
         <v>463</v>
       </c>
@@ -18209,7 +18273,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
         <v>464</v>
       </c>
@@ -18247,7 +18311,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
         <v>465</v>
       </c>
@@ -18285,7 +18349,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
         <v>466</v>
       </c>
@@ -18323,7 +18387,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468" s="4">
         <v>467</v>
       </c>
@@ -18361,7 +18425,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
         <v>468</v>
       </c>
@@ -18399,7 +18463,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470" s="4">
         <v>469</v>
       </c>
@@ -18437,7 +18501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>470</v>
       </c>
@@ -18475,7 +18539,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
         <v>471</v>
       </c>
@@ -18513,7 +18577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
         <v>472</v>
       </c>
@@ -18551,7 +18615,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474" s="4">
         <v>473</v>
       </c>
@@ -18589,7 +18653,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
         <v>474</v>
       </c>
@@ -18627,7 +18691,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
         <v>475</v>
       </c>
@@ -18665,7 +18729,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
         <v>476</v>
       </c>
@@ -18703,7 +18767,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478" s="4">
         <v>477</v>
       </c>
@@ -18741,7 +18805,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479" s="4">
         <v>478</v>
       </c>
@@ -18779,7 +18843,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480" s="4">
         <v>479</v>
       </c>
@@ -18817,7 +18881,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" s="4">
         <v>480</v>
       </c>
@@ -18855,7 +18919,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A482" s="4">
         <v>481</v>
       </c>
@@ -18893,7 +18957,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" s="4">
         <v>482</v>
       </c>
@@ -18931,7 +18995,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484" s="4">
         <v>483</v>
       </c>
@@ -18969,7 +19033,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" s="4">
         <v>484</v>
       </c>
@@ -19007,7 +19071,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486" s="4">
         <v>485</v>
       </c>
@@ -19045,7 +19109,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" s="4">
         <v>486</v>
       </c>
@@ -19083,7 +19147,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" s="4">
         <v>487</v>
       </c>
@@ -19121,7 +19185,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489" s="4">
         <v>488</v>
       </c>
@@ -19159,7 +19223,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" s="4">
         <v>489</v>
       </c>
@@ -19197,7 +19261,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -19235,7 +19299,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" s="4">
         <v>491</v>
       </c>
@@ -19273,7 +19337,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -19311,7 +19375,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" s="4">
         <v>493</v>
       </c>
@@ -19349,7 +19413,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -19387,7 +19451,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -19425,7 +19489,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -19463,7 +19527,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" s="4">
         <v>497</v>
       </c>
@@ -19501,7 +19565,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -19539,7 +19603,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" s="4">
         <v>499</v>
       </c>
@@ -19577,7 +19641,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -19615,7 +19679,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" s="4">
         <v>501</v>
       </c>
@@ -19653,7 +19717,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" s="4">
         <v>502</v>
       </c>
@@ -19691,7 +19755,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" s="4">
         <v>503</v>
       </c>
@@ -19729,7 +19793,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" s="4">
         <v>504</v>
       </c>
@@ -19767,7 +19831,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" s="4">
         <v>505</v>
       </c>
@@ -19805,7 +19869,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" s="4">
         <v>506</v>
       </c>
@@ -19843,7 +19907,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" s="4">
         <v>507</v>
       </c>
@@ -19881,7 +19945,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" s="4">
         <v>508</v>
       </c>
@@ -19919,7 +19983,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" s="4">
         <v>509</v>
       </c>
@@ -19957,7 +20021,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" s="4">
         <v>510</v>
       </c>
@@ -19995,7 +20059,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" s="4">
         <v>511</v>
       </c>
@@ -20033,7 +20097,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" s="4">
         <v>512</v>
       </c>
@@ -20071,7 +20135,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" s="4">
         <v>513</v>
       </c>
@@ -20109,7 +20173,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" s="4">
         <v>514</v>
       </c>
@@ -20147,7 +20211,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" s="4">
         <v>515</v>
       </c>
@@ -20185,7 +20249,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" s="4">
         <v>516</v>
       </c>
@@ -20223,7 +20287,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" s="4">
         <v>517</v>
       </c>
@@ -20261,7 +20325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" s="4">
         <v>518</v>
       </c>
@@ -20299,7 +20363,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" s="4">
         <v>519</v>
       </c>
@@ -20337,7 +20401,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" s="4">
         <v>520</v>
       </c>
@@ -20375,7 +20439,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" s="4">
         <v>521</v>
       </c>
@@ -20413,7 +20477,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" s="4">
         <v>522</v>
       </c>
@@ -20451,7 +20515,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" s="4">
         <v>523</v>
       </c>
@@ -20489,7 +20553,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" s="4">
         <v>524</v>
       </c>
@@ -20527,7 +20591,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" s="4">
         <v>525</v>
       </c>
@@ -20565,7 +20629,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" s="4">
         <v>526</v>
       </c>
@@ -20603,7 +20667,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" s="4">
         <v>527</v>
       </c>
@@ -20641,7 +20705,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" s="4">
         <v>528</v>
       </c>
@@ -20679,7 +20743,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" s="4">
         <v>529</v>
       </c>
@@ -20717,7 +20781,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" s="4">
         <v>530</v>
       </c>
@@ -20755,7 +20819,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" s="4">
         <v>531</v>
       </c>
@@ -20793,7 +20857,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" s="4">
         <v>532</v>
       </c>
@@ -20831,7 +20895,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" s="4">
         <v>533</v>
       </c>
@@ -20869,7 +20933,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" s="4">
         <v>534</v>
       </c>
@@ -20907,7 +20971,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" s="4">
         <v>535</v>
       </c>
@@ -20945,7 +21009,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" s="4">
         <v>536</v>
       </c>
@@ -20983,7 +21047,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" s="4">
         <v>537</v>
       </c>
@@ -21021,7 +21085,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" s="4">
         <v>538</v>
       </c>
@@ -21059,7 +21123,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" s="4">
         <v>539</v>
       </c>
@@ -21097,7 +21161,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" s="4">
         <v>540</v>
       </c>
@@ -21135,7 +21199,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" s="4">
         <v>541</v>
       </c>
@@ -21173,7 +21237,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" s="4">
         <v>542</v>
       </c>
@@ -21211,7 +21275,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" s="4">
         <v>543</v>
       </c>
@@ -21249,7 +21313,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" s="4">
         <v>544</v>
       </c>
@@ -21287,7 +21351,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" s="4">
         <v>545</v>
       </c>
@@ -21325,7 +21389,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547" s="4">
         <v>546</v>
       </c>
@@ -21363,7 +21427,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A548" s="4">
         <v>547</v>
       </c>
@@ -21401,7 +21465,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549" s="4">
         <v>548</v>
       </c>
@@ -21439,7 +21503,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550" s="4">
         <v>549</v>
       </c>
@@ -21477,7 +21541,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551" s="4">
         <v>550</v>
       </c>
@@ -21515,7 +21579,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552" s="4">
         <v>551</v>
       </c>
@@ -21553,7 +21617,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A553" s="4">
         <v>552</v>
       </c>
@@ -21591,7 +21655,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554" s="4">
         <v>553</v>
       </c>
@@ -21629,7 +21693,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555" s="4">
         <v>554</v>
       </c>
@@ -21667,7 +21731,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556" s="4">
         <v>555</v>
       </c>
@@ -21705,7 +21769,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557" s="4">
         <v>556</v>
       </c>
@@ -21743,7 +21807,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A558" s="4">
         <v>557</v>
       </c>
@@ -21781,7 +21845,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559" s="4">
         <v>558</v>
       </c>
@@ -21819,7 +21883,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560" s="4">
         <v>559</v>
       </c>
@@ -21857,7 +21921,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" s="4">
         <v>560</v>
       </c>
@@ -21895,7 +21959,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562" s="4">
         <v>561</v>
       </c>
@@ -21933,7 +21997,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A563" s="4">
         <v>562</v>
       </c>
@@ -21971,7 +22035,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A564" s="4">
         <v>563</v>
       </c>
@@ -22009,7 +22073,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A565" s="4">
         <v>564</v>
       </c>
@@ -22047,7 +22111,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A566" s="4">
         <v>565</v>
       </c>
@@ -22085,7 +22149,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A567" s="4">
         <v>566</v>
       </c>
@@ -22123,7 +22187,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A568" s="4">
         <v>567</v>
       </c>
@@ -22161,7 +22225,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A569" s="4">
         <v>568</v>
       </c>
@@ -22199,7 +22263,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A570" s="4">
         <v>569</v>
       </c>
@@ -22237,7 +22301,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A571" s="4">
         <v>570</v>
       </c>
@@ -22275,7 +22339,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A572" s="4">
         <v>571</v>
       </c>
@@ -22313,7 +22377,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A573" s="4">
         <v>572</v>
       </c>
@@ -22351,7 +22415,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A574" s="4">
         <v>573</v>
       </c>
@@ -22389,7 +22453,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A575" s="4">
         <v>574</v>
       </c>
@@ -22427,7 +22491,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A576" s="4">
         <v>575</v>
       </c>
@@ -22465,7 +22529,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A577" s="4">
         <v>576</v>
       </c>
@@ -22503,7 +22567,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A578" s="4">
         <v>577</v>
       </c>
@@ -22541,7 +22605,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A579" s="4">
         <v>578</v>
       </c>
@@ -22579,7 +22643,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A580" s="4">
         <v>579</v>
       </c>
@@ -22617,7 +22681,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A581" s="4">
         <v>580</v>
       </c>
@@ -22655,7 +22719,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A582" s="4">
         <v>581</v>
       </c>
@@ -22693,7 +22757,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A583" s="4">
         <v>582</v>
       </c>
@@ -22731,7 +22795,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A584" s="4">
         <v>583</v>
       </c>
@@ -22769,7 +22833,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A585" s="4">
         <v>584</v>
       </c>
@@ -22807,7 +22871,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A586" s="4">
         <v>585</v>
       </c>
@@ -22845,7 +22909,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A587" s="4">
         <v>586</v>
       </c>
@@ -22883,7 +22947,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A588" s="4">
         <v>587</v>
       </c>
@@ -22921,7 +22985,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A589" s="4">
         <v>588</v>
       </c>
@@ -22959,7 +23023,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A590" s="4">
         <v>589</v>
       </c>
@@ -22997,7 +23061,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A591" s="4">
         <v>590</v>
       </c>
@@ -23035,7 +23099,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A592" s="4">
         <v>591</v>
       </c>
@@ -23073,7 +23137,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A593" s="4">
         <v>592</v>
       </c>
@@ -23111,7 +23175,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A594" s="4">
         <v>593</v>
       </c>
@@ -23149,7 +23213,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A595" s="4">
         <v>594</v>
       </c>
@@ -23187,7 +23251,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A596" s="4">
         <v>595</v>
       </c>
@@ -23225,7 +23289,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A597" s="4">
         <v>596</v>
       </c>
@@ -23263,7 +23327,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A598" s="4">
         <v>597</v>
       </c>
@@ -23301,7 +23365,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A599" s="4">
         <v>598</v>
       </c>
@@ -23339,7 +23403,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A600" s="4">
         <v>599</v>
       </c>
@@ -23377,7 +23441,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A601" s="4">
         <v>600</v>
       </c>
@@ -23415,7 +23479,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A602" s="4">
         <v>601</v>
       </c>
@@ -23453,7 +23517,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A603" s="4">
         <v>602</v>
       </c>
@@ -23491,7 +23555,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A604" s="4">
         <v>603</v>
       </c>
@@ -23529,7 +23593,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A605" s="4">
         <v>604</v>
       </c>
@@ -23567,7 +23631,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A606" s="4">
         <v>605</v>
       </c>
@@ -23605,7 +23669,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A607" s="4">
         <v>606</v>
       </c>
@@ -23643,7 +23707,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A608" s="4">
         <v>607</v>
       </c>
@@ -23681,7 +23745,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A609" s="4">
         <v>608</v>
       </c>
@@ -23719,7 +23783,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A610" s="4">
         <v>609</v>
       </c>
@@ -23757,7 +23821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A611" s="4">
         <v>610</v>
       </c>
@@ -23795,7 +23859,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A612" s="4">
         <v>611</v>
       </c>
@@ -23833,7 +23897,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A613" s="4">
         <v>612</v>
       </c>
@@ -23871,7 +23935,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A614" s="4">
         <v>613</v>
       </c>
@@ -23909,7 +23973,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A615" s="4">
         <v>614</v>
       </c>
@@ -23947,7 +24011,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A616" s="4">
         <v>615</v>
       </c>
@@ -23985,7 +24049,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A617" s="4">
         <v>616</v>
       </c>
@@ -24023,7 +24087,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A618" s="4">
         <v>617</v>
       </c>
@@ -24061,7 +24125,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A619" s="4">
         <v>618</v>
       </c>
@@ -24099,7 +24163,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A620" s="4">
         <v>619</v>
       </c>
@@ -24137,7 +24201,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A621" s="4">
         <v>620</v>
       </c>
@@ -24175,7 +24239,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A622" s="4">
         <v>621</v>
       </c>
@@ -24213,7 +24277,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A623" s="4">
         <v>622</v>
       </c>
@@ -24251,7 +24315,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A624" s="4">
         <v>623</v>
       </c>
@@ -24289,7 +24353,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A625" s="4">
         <v>624</v>
       </c>
@@ -24327,7 +24391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A626" s="4">
         <v>625</v>
       </c>
@@ -24365,7 +24429,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A627" s="4">
         <v>626</v>
       </c>
@@ -24403,7 +24467,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A628" s="4">
         <v>627</v>
       </c>
@@ -24441,7 +24505,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A629" s="4">
         <v>628</v>
       </c>
@@ -24479,7 +24543,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A630" s="4">
         <v>629</v>
       </c>
@@ -24517,7 +24581,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A631" s="4">
         <v>630</v>
       </c>
@@ -24555,7 +24619,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A632" s="4">
         <v>631</v>
       </c>
@@ -24593,7 +24657,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A633" s="4">
         <v>632</v>
       </c>
@@ -24631,7 +24695,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A634" s="4">
         <v>633</v>
       </c>
@@ -24669,7 +24733,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A635" s="4">
         <v>634</v>
       </c>
@@ -24707,7 +24771,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A636" s="4">
         <v>635</v>
       </c>
@@ -24745,7 +24809,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A637" s="4">
         <v>636</v>
       </c>
@@ -24783,7 +24847,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A638" s="4">
         <v>637</v>
       </c>
@@ -24821,7 +24885,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A639" s="4">
         <v>638</v>
       </c>
@@ -24859,7 +24923,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A640" s="4">
         <v>639</v>
       </c>
@@ -24897,7 +24961,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A641" s="4">
         <v>640</v>
       </c>
@@ -24935,7 +24999,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A642" s="4">
         <v>641</v>
       </c>
@@ -24973,7 +25037,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A643" s="4">
         <v>642</v>
       </c>
@@ -25011,7 +25075,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A644" s="4">
         <v>643</v>
       </c>
@@ -25049,7 +25113,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A645" s="4">
         <v>644</v>
       </c>
@@ -25087,7 +25151,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A646" s="4">
         <v>645</v>
       </c>
@@ -25125,7 +25189,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A647" s="4">
         <v>646</v>
       </c>
@@ -25163,7 +25227,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A648" s="4">
         <v>647</v>
       </c>
@@ -25201,7 +25265,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A649" s="4">
         <v>648</v>
       </c>
@@ -25239,7 +25303,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A650" s="4">
         <v>649</v>
       </c>
@@ -25277,7 +25341,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A651" s="4">
         <v>650</v>
       </c>
@@ -25315,7 +25379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A652" s="4">
         <v>651</v>
       </c>
@@ -25353,7 +25417,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A653" s="4">
         <v>652</v>
       </c>
@@ -25391,7 +25455,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A654" s="4">
         <v>653</v>
       </c>
@@ -25429,7 +25493,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A655" s="4">
         <v>654</v>
       </c>
@@ -25467,7 +25531,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A656" s="4">
         <v>655</v>
       </c>
@@ -25505,7 +25569,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A657" s="4">
         <v>656</v>
       </c>
@@ -25543,7 +25607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A658" s="4">
         <v>657</v>
       </c>
@@ -25581,7 +25645,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A659" s="4">
         <v>658</v>
       </c>
@@ -25619,7 +25683,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A660" s="4">
         <v>659</v>
       </c>
@@ -25657,7 +25721,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A661" s="4">
         <v>660</v>
       </c>
@@ -25695,7 +25759,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A662" s="4">
         <v>661</v>
       </c>
@@ -25733,7 +25797,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A663" s="4">
         <v>662</v>
       </c>
@@ -25771,7 +25835,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A664" s="4">
         <v>663</v>
       </c>
@@ -25809,7 +25873,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A665" s="4">
         <v>664</v>
       </c>
@@ -25847,7 +25911,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A666" s="4">
         <v>665</v>
       </c>
@@ -25885,7 +25949,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A667" s="4">
         <v>666</v>
       </c>
@@ -25923,7 +25987,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A668" s="4">
         <v>667</v>
       </c>
@@ -25961,7 +26025,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A669" s="4">
         <v>668</v>
       </c>
@@ -25999,7 +26063,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A670" s="4">
         <v>669</v>
       </c>
@@ -26037,7 +26101,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A671" s="4">
         <v>670</v>
       </c>
@@ -26075,7 +26139,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A672" s="4">
         <v>671</v>
       </c>
@@ -26113,7 +26177,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A673" s="4">
         <v>672</v>
       </c>
@@ -26151,7 +26215,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A674" s="4">
         <v>673</v>
       </c>
@@ -26189,7 +26253,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A675" s="4">
         <v>674</v>
       </c>
@@ -26227,7 +26291,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A676" s="4">
         <v>675</v>
       </c>
@@ -26265,7 +26329,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A677" s="4">
         <v>676</v>
       </c>
@@ -26303,7 +26367,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A678" s="4">
         <v>677</v>
       </c>
@@ -26341,7 +26405,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A679" s="4">
         <v>678</v>
       </c>
@@ -26379,7 +26443,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A680" s="4">
         <v>679</v>
       </c>
@@ -26417,7 +26481,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A681" s="4">
         <v>680</v>
       </c>
@@ -26455,7 +26519,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A682" s="4">
         <v>681</v>
       </c>
@@ -26493,7 +26557,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A683" s="4">
         <v>682</v>
       </c>
@@ -26531,7 +26595,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A684" s="4">
         <v>683</v>
       </c>
@@ -26569,7 +26633,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A685" s="4">
         <v>684</v>
       </c>
@@ -26607,7 +26671,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A686" s="4">
         <v>685</v>
       </c>
@@ -26645,7 +26709,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A687" s="4">
         <v>686</v>
       </c>
@@ -26683,7 +26747,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A688" s="4">
         <v>687</v>
       </c>
@@ -26721,7 +26785,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A689" s="4">
         <v>688</v>
       </c>
@@ -26759,7 +26823,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A690" s="4">
         <v>689</v>
       </c>
@@ -26797,7 +26861,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A691" s="4">
         <v>690</v>
       </c>
@@ -26835,7 +26899,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A692" s="4">
         <v>691</v>
       </c>
@@ -26873,7 +26937,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A693" s="4">
         <v>692</v>
       </c>
@@ -26911,7 +26975,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A694" s="4">
         <v>693</v>
       </c>
@@ -26949,7 +27013,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A695" s="4">
         <v>694</v>
       </c>
@@ -26987,7 +27051,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A696" s="4">
         <v>695</v>
       </c>
@@ -27025,7 +27089,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A697" s="4">
         <v>696</v>
       </c>
@@ -27063,7 +27127,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A698" s="4">
         <v>697</v>
       </c>
@@ -27101,7 +27165,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A699" s="4">
         <v>698</v>
       </c>
@@ -27139,7 +27203,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A700" s="4">
         <v>699</v>
       </c>
@@ -27177,7 +27241,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A701" s="4">
         <v>700</v>
       </c>
@@ -27215,7 +27279,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A702" s="4">
         <v>701</v>
       </c>
@@ -27253,7 +27317,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A703" s="4">
         <v>702</v>
       </c>
@@ -27291,7 +27355,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A704" s="4">
         <v>703</v>
       </c>
@@ -27329,7 +27393,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A705" s="4">
         <v>704</v>
       </c>
@@ -27367,7 +27431,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A706" s="4">
         <v>705</v>
       </c>
@@ -27405,7 +27469,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A707" s="4">
         <v>706</v>
       </c>
@@ -27443,7 +27507,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A708" s="4">
         <v>707</v>
       </c>
@@ -27481,7 +27545,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A709" s="4">
         <v>708</v>
       </c>
@@ -27519,7 +27583,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A710" s="4">
         <v>709</v>
       </c>
@@ -27557,7 +27621,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A711" s="4">
         <v>710</v>
       </c>
@@ -27595,7 +27659,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A712" s="4">
         <v>711</v>
       </c>
@@ -27633,7 +27697,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A713" s="4">
         <v>712</v>
       </c>
@@ -27671,7 +27735,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A714" s="4">
         <v>713</v>
       </c>
@@ -27709,7 +27773,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A715" s="4">
         <v>714</v>
       </c>
@@ -27747,7 +27811,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A716" s="4">
         <v>715</v>
       </c>
@@ -27785,7 +27849,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A717" s="4">
         <v>716</v>
       </c>
@@ -27823,7 +27887,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A718" s="4">
         <v>717</v>
       </c>
@@ -27861,7 +27925,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A719" s="4">
         <v>718</v>
       </c>
@@ -27899,7 +27963,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A720" s="4">
         <v>719</v>
       </c>
@@ -27937,7 +28001,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A721" s="4">
         <v>720</v>
       </c>
@@ -27975,7 +28039,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A722" s="4">
         <v>721</v>
       </c>
@@ -28013,7 +28077,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A723" s="4">
         <v>722</v>
       </c>
@@ -28051,7 +28115,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A724" s="4">
         <v>723</v>
       </c>
@@ -28089,7 +28153,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A725" s="4">
         <v>724</v>
       </c>
@@ -28127,7 +28191,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A726" s="4">
         <v>725</v>
       </c>
@@ -28165,7 +28229,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A727" s="4">
         <v>726</v>
       </c>
@@ -28203,7 +28267,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A728" s="4">
         <v>727</v>
       </c>
@@ -28241,7 +28305,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A729" s="4">
         <v>728</v>
       </c>
@@ -28279,7 +28343,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A730" s="4">
         <v>729</v>
       </c>
@@ -28317,7 +28381,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A731" s="4">
         <v>730</v>
       </c>
@@ -28355,7 +28419,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A732" s="4">
         <v>731</v>
       </c>
@@ -28393,7 +28457,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A733" s="4">
         <v>732</v>
       </c>
@@ -28431,7 +28495,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A734" s="4">
         <v>733</v>
       </c>
@@ -28469,7 +28533,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A735" s="4">
         <v>734</v>
       </c>
@@ -28507,7 +28571,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A736" s="4">
         <v>735</v>
       </c>
@@ -28545,7 +28609,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A737" s="4">
         <v>736</v>
       </c>
@@ -28583,7 +28647,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A738" s="4">
         <v>737</v>
       </c>
@@ -28621,7 +28685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A739" s="4">
         <v>738</v>
       </c>
@@ -28659,7 +28723,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A740" s="4">
         <v>739</v>
       </c>
@@ -28697,7 +28761,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A741" s="4">
         <v>740</v>
       </c>
@@ -28735,7 +28799,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A742" s="4">
         <v>741</v>
       </c>
@@ -28773,7 +28837,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A743" s="4">
         <v>742</v>
       </c>
@@ -28811,7 +28875,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A744" s="4">
         <v>743</v>
       </c>
@@ -28849,7 +28913,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A745" s="4">
         <v>744</v>
       </c>
@@ -28887,7 +28951,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A746" s="4">
         <v>745</v>
       </c>
@@ -28925,7 +28989,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A747" s="4">
         <v>746</v>
       </c>
@@ -28963,7 +29027,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A748" s="4">
         <v>747</v>
       </c>
@@ -29001,7 +29065,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A749" s="4">
         <v>748</v>
       </c>
@@ -29039,7 +29103,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A750" s="4">
         <v>749</v>
       </c>
@@ -29077,7 +29141,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A751" s="4">
         <v>750</v>
       </c>
@@ -29115,7 +29179,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A752" s="4">
         <v>751</v>
       </c>
@@ -29153,7 +29217,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A753" s="4">
         <v>752</v>
       </c>
@@ -29191,7 +29255,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A754" s="4">
         <v>753</v>
       </c>
@@ -29229,7 +29293,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A755" s="4">
         <v>754</v>
       </c>
@@ -29267,7 +29331,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A756" s="4">
         <v>755</v>
       </c>
@@ -29305,7 +29369,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A757" s="4">
         <v>756</v>
       </c>
@@ -29343,7 +29407,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A758" s="4">
         <v>757</v>
       </c>
@@ -29381,7 +29445,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A759" s="4">
         <v>758</v>
       </c>
@@ -29419,7 +29483,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A760" s="4">
         <v>759</v>
       </c>
@@ -29457,7 +29521,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A761" s="4">
         <v>760</v>
       </c>
@@ -29495,7 +29559,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A762" s="4">
         <v>761</v>
       </c>
@@ -29533,7 +29597,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A763" s="4">
         <v>762</v>
       </c>
@@ -29571,7 +29635,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A764" s="4">
         <v>763</v>
       </c>
@@ -29609,7 +29673,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A765" s="4">
         <v>764</v>
       </c>
@@ -29647,7 +29711,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A766" s="4">
         <v>765</v>
       </c>
@@ -29685,7 +29749,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A767" s="4">
         <v>766</v>
       </c>
@@ -29723,7 +29787,7 @@
         <v>3825</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A768" s="4">
         <v>767</v>
       </c>
@@ -29761,7 +29825,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A769" s="4">
         <v>768</v>
       </c>
@@ -29799,7 +29863,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A770" s="4">
         <v>769</v>
       </c>
@@ -29837,7 +29901,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A771" s="4">
         <v>770</v>
       </c>
@@ -29875,7 +29939,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A772" s="4">
         <v>771</v>
       </c>
@@ -29913,7 +29977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A773" s="4">
         <v>772</v>
       </c>
@@ -29951,7 +30015,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A774" s="4">
         <v>773</v>
       </c>
@@ -29989,7 +30053,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A775" s="4">
         <v>774</v>
       </c>
@@ -30027,7 +30091,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A776" s="4">
         <v>775</v>
       </c>
@@ -30065,7 +30129,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A777" s="4">
         <v>776</v>
       </c>
@@ -30103,7 +30167,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A778" s="4">
         <v>777</v>
       </c>
@@ -30141,7 +30205,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A779" s="4">
         <v>778</v>
       </c>
@@ -30179,148 +30243,148 @@
         <v>360</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L780" s="2"/>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L781" s="2"/>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L782" s="2"/>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L783" s="2"/>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L784" s="2"/>
     </row>
-    <row r="785" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="785" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L785" s="2"/>
     </row>
-    <row r="786" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="786" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L786" s="2"/>
     </row>
-    <row r="787" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="787" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L787" s="2"/>
     </row>
-    <row r="788" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="788" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L788" s="2"/>
     </row>
-    <row r="789" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="789" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L789" s="2"/>
     </row>
-    <row r="790" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="790" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L790" s="2"/>
     </row>
-    <row r="791" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="791" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L791" s="2"/>
     </row>
-    <row r="792" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="792" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L792" s="2"/>
     </row>
-    <row r="793" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="793" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L793" s="2"/>
     </row>
-    <row r="794" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="794" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L794" s="2"/>
     </row>
-    <row r="795" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="795" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L795" s="2"/>
     </row>
-    <row r="796" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="796" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L796" s="2"/>
     </row>
-    <row r="797" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="797" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L797" s="2"/>
     </row>
-    <row r="798" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="798" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L798" s="2"/>
     </row>
-    <row r="799" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="799" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L799" s="2"/>
     </row>
-    <row r="800" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="800" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L800" s="2"/>
     </row>
-    <row r="801" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="801" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L801" s="2"/>
     </row>
-    <row r="802" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="802" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L802" s="2"/>
     </row>
-    <row r="803" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="803" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L803" s="2"/>
     </row>
-    <row r="804" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="804" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L804" s="2"/>
     </row>
-    <row r="805" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="805" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L805" s="2"/>
     </row>
-    <row r="806" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="806" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L806" s="2"/>
     </row>
-    <row r="807" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="807" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L807" s="2"/>
     </row>
-    <row r="808" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="808" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L808" s="2"/>
     </row>
-    <row r="809" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="809" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L809" s="2"/>
     </row>
-    <row r="810" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="810" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L810" s="2"/>
     </row>
-    <row r="811" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="811" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L811" s="2"/>
     </row>
-    <row r="812" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="812" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L812" s="2"/>
     </row>
-    <row r="813" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="813" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L813" s="2"/>
     </row>
-    <row r="814" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="814" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L814" s="2"/>
     </row>
-    <row r="815" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="815" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L815" s="2"/>
     </row>
-    <row r="816" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="816" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L816" s="2"/>
     </row>
-    <row r="817" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="817" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L817" s="2"/>
     </row>
-    <row r="818" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="818" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L818" s="2"/>
     </row>
-    <row r="819" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="819" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L819" s="2"/>
     </row>
-    <row r="820" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="820" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L820" s="2"/>
     </row>
-    <row r="821" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="821" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L821" s="2"/>
     </row>
-    <row r="822" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="822" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L822" s="2"/>
     </row>
-    <row r="823" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="823" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L823" s="2"/>
     </row>
-    <row r="824" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="824" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L824" s="2"/>
     </row>
-    <row r="825" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="825" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L825" s="2"/>
     </row>
-    <row r="826" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="826" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L826" s="2"/>
     </row>
-    <row r="827" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="827" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L827" s="2"/>
     </row>
   </sheetData>
@@ -30328,5 +30392,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>